--- a/data/抒情簿——哲学部.xlsx
+++ b/data/抒情簿——哲学部.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555"/>
+    <workbookView windowWidth="14062" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$AO$1359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$AO$1369</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="1396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="1412">
   <si>
     <t>抒情簿——哲学部</t>
   </si>
@@ -5777,6 +5777,76 @@
   </si>
   <si>
     <t>唐突想起我严苛可敬的一位老师，在假设中我展开了激烈的反思，而不得不回到现实看现在与刚才的幻想的精神差异。我问自己：是什么让我的思想到达了某种程度的成功？开玩笑地说，我脑海里浮现出来一个狂妄自大的形象。但认真来评价，且注意，不是因果而是现象描述地解释，我认为这与我听取长辈的建议、自我判断后的接受有关。自从陷入自由的泥潭之后，生命中“他者”的缺乏是一个不可忽视的漏洞。远而观之，人生的道路上谁会成为前行的伙伴？又该对此抱以怎样的期待？思索半晌，然孰知轻重。——2026.1.31</t>
+  </si>
+  <si>
+    <t>（别人的故事都讲完了
+现在，来讲一讲你自己的故事吧。）
+——2026.3.8摘于lz作品《Universal Dilemma》</t>
+  </si>
+  <si>
+    <t>　　近日的生活可能是重复、回顾、组合无常，大家却忘记了心中始源的力量。原始的意境、原始的赏析、原始的审美反应……我是否是在阴影之下忘记了部分我作为人的存在？
+　　很遗憾，从开始行动到确认自己的能力有限与渺小，都需要漫长的时间。这意味着人生的意义有限吗？吗？我叩问。
+　　人类与人，交往间是一次次的失之交臂吗？他者价值判断中我所认为的缺陷，仿佛是影视剧不可逆结局的板上钉。我清楚我之局限，又要深思：我的几乎不可变的缺陷是否有改正的希望？
+　　错了，始源的力量是对事物最初的——本能美感、本能思索，并非不曾拥有！
+　　人生的意义的火炬我已经点燃出来，但是我有必要谨慎判断，我为自己、为身边的人，怎样才能创造出最大的价值？这本身不可衡量。但是，构成我们平日、每月、余年的，只有平常的行为吗？
+　　叶子几乎不会有两片相同的，世界观、价值观、人生观也是如此！我们永远与他人离线聊天。如果我们找到相同，基于的事、基于的物，只是那些表层吗……我知道、我体会这些欢愉，但我依然期盼真正的同行者。但，也许更多时候，大家仍然是交错。并非没有交集，只是时空错位，我看着来到过去的我的你，我奔向过去的你。我期盼未来的我成为你，你期盼未来的你成为我。
+——2026.3.19作，2026.3.19遗忘</t>
+  </si>
+  <si>
+    <t>A：你的走路姿势好机械啊。
+B：是我有意为之，我意识到自己的走路姿势机械。
+A：是不是你认为所有你的有意为之必须被你自己知道？
+B：如果哪一天我意识不到这一点，那么我就堕落了。——2026.3.25</t>
+  </si>
+  <si>
+    <t>A：如果游戏把游戏性发挥到了极致，那么游戏将很难适应严肃的题材。
+B：当一款游戏把娱乐化、快感驱动的游戏性发挥到极致时，它很难再承载严肃、沉重、现实的题材。
+C：以快感为核心的极致游戏性，会消解严肃；
+以表达为核心的极致游戏性，会强化严肃。——2026.3.27（B、C内容由AI生成）</t>
+  </si>
+  <si>
+    <t>Each going well is living a fake life. Each having reflections in sudden is just a ridiculous play.——2026.4.3</t>
+  </si>
+  <si>
+    <t>　　进入大学以后，大部分的时间我几乎都是在看手机电脑，“输入”可以说占据了全部。现在我在学校里走走，也要开动脑筋，这是与之相对应的“输出”。输入、输出……难道说……我是控制台？不开玩笑，之所以有这些想法，是因为我想到了之前的问题，也是大家经常提及的：怎么到了大学生活反而没有记忆点了。看样子是“输出”太少了。又想起：学而不思则罔，思而不学则殆。我忘了“罔”是何意、“殆”是何意，我只知道今天我有相关的思考。
+　　我不敢说我现在有什么高度、或者以某种高高的姿态去看校园内的纪念石与上面的“学思并进，奋楫笃行”，但我敢说，今天的我有足够的自由，以这样的自信去看着它。——2026.4.6</t>
+  </si>
+  <si>
+    <t>创作不是“输出结果”，而是“做出选择的过程”。——2026.4.14摘于DeepSeek</t>
+  </si>
+  <si>
+    <t>The one loses its present in real life.——2026.4.24自评</t>
+  </si>
+  <si>
+    <t>坚持、毅力是否会对人对美好事物的本能洞察造成损坏？——2026.4.29问，回复2022.2.17</t>
+  </si>
+  <si>
+    <t>依然是在操场上散心，看着被众多灯光打出的影子，我突然仿佛认为：那一众重影是等着被科技进步拯救自己心愿的芸芸众生，而正在行走的我是现在的唯一时刻。——2026.4.29</t>
+  </si>
+  <si>
+    <t>人正是每天都有无限的思绪才能活下去啊。——2026.5.25</t>
+  </si>
+  <si>
+    <t>X：你觉得有的人能够一直“生活”下去是因为他们发现了什么更好的定理或者真理吗？
+Y：不是，是因为他们拥有无限的思绪，这种精神力量是源源不断的。
+X：这些人有时觉得他们因此受到困扰，你怎么看？
+Y：即便是焦虑，也强于堕落于虚空的焦虑叙事与重复叙事。无限的思绪的宝贵，在于它永远在生成的行为。
+X：好像有点奇怪，我还没问你什么是无限的思绪。
+Y：它不是一种对问题的思考、不是具体问题或工程项目的推进，它是对生活的思考。如果一个人要对什么目标反复叩问其意义，且没有人阻止这个人，这是一件非常恐怖的事情。无限的思绪贵在它不束缚于有限的问题。这听上去似乎不太“无限”，但是思绪是不会被单个问题束缚住的，否则那是思维。
+——2026.5.25撰于凌晨</t>
+  </si>
+  <si>
+    <t>夏天来了，终于可以感受到自然的暖风抚摸我的全身了。——2026.5.30</t>
+  </si>
+  <si>
+    <t>大语言模型把世界很多规律压缩成相关性（这一条规律来运行）。
+语言具有自反性，这导致了人类的思维。——2026.6.3摘自视频《世界模型、超现实世界与动词波》</t>
+  </si>
+  <si>
+    <t>语言模型，是以那种最容易被确认的相关性，来代替了说不清楚的因果性，（这）产生了巨大效率。因为只有一条规律来运行的话，这个效率一定是非常高的，不会有其他规律来“捣乱”。——2026.6.3摘自视频《世界模型、超现实世界与动词波》</t>
+  </si>
+  <si>
+    <t>发明这语言大模型的科学家是天才，他们发现了可以用经验论的方法，去处理非经验对象。——2026.6.3摘自视频《世界模型、超现实世界与动词波》</t>
   </si>
 </sst>
 </file>
@@ -6011,6 +6081,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <u/>
       <sz val="14"/>
@@ -6021,13 +6098,6 @@
       <u/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -7097,7 +7167,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO1369"/>
+  <dimension ref="A1:AO1384"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.1"/>
   <cols>
     <col min="1" max="1" width="5.87610619469027" style="2" customWidth="1"/>
@@ -39890,7 +39960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1361" ht="95.65" spans="1:31">
+    <row r="1361" ht="95.65" spans="1:35">
       <c r="A1361" s="2">
         <v>1357</v>
       </c>
@@ -39922,7 +39992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1362" ht="248.65" spans="1:31">
+    <row r="1362" ht="248.65" spans="1:35">
       <c r="A1362" s="2">
         <v>1358</v>
       </c>
@@ -39948,7 +40018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1363" ht="38.25" spans="1:31">
+    <row r="1363" ht="38.25" spans="1:35">
       <c r="A1363" s="2">
         <v>1359</v>
       </c>
@@ -39977,7 +40047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1364" ht="57.4" spans="1:31">
+    <row r="1364" ht="57.4" spans="1:35">
       <c r="A1364" s="2">
         <v>1360</v>
       </c>
@@ -40003,7 +40073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1365" ht="114.75" spans="1:31">
+    <row r="1365" ht="114.75" spans="1:35">
       <c r="A1365" s="2">
         <v>1361</v>
       </c>
@@ -40029,7 +40099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1366" ht="38.25" spans="1:31">
+    <row r="1366" ht="38.25" spans="1:35">
       <c r="A1366" s="2">
         <v>1362</v>
       </c>
@@ -40052,7 +40122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1367" ht="210.4" spans="1:31">
+    <row r="1367" ht="210.4" spans="1:35">
       <c r="A1367" s="2">
         <v>1363</v>
       </c>
@@ -40074,23 +40144,481 @@
       <c r="O1367" s="9">
         <v>1</v>
       </c>
-      <c r="P1367" s="9"/>
       <c r="V1367" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="1368" spans="1:31">
+    <row r="1368" ht="57.4" spans="1:35">
       <c r="A1368" s="2">
         <v>1364</v>
       </c>
-    </row>
-    <row r="1369" spans="1:31">
+      <c r="B1368" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C1368" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1368" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1368" s="6">
+        <v>8</v>
+      </c>
+      <c r="F1368" s="2">
+        <v>1</v>
+      </c>
+      <c r="O1368" s="9">
+        <v>1</v>
+      </c>
+      <c r="S1368" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1369" ht="409.5" spans="1:35">
       <c r="A1369" s="2">
         <v>1365</v>
       </c>
+      <c r="B1369" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C1369" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1369" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1369" s="6">
+        <v>19</v>
+      </c>
+      <c r="F1369" s="2">
+        <v>0</v>
+      </c>
+      <c r="R1369" s="10">
+        <v>1</v>
+      </c>
+      <c r="S1369" s="10">
+        <v>1</v>
+      </c>
+      <c r="U1369" s="10">
+        <v>1</v>
+      </c>
+      <c r="V1369" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD1369" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF1369" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1370" ht="114.75" spans="1:35">
+      <c r="A1370" s="2">
+        <v>1366</v>
+      </c>
+      <c r="B1370" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1370" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1370" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1370" s="6">
+        <v>25</v>
+      </c>
+      <c r="F1370" s="2">
+        <v>0</v>
+      </c>
+      <c r="O1370" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1371" ht="133.9" spans="1:35">
+      <c r="A1371" s="2">
+        <v>1367</v>
+      </c>
+      <c r="B1371" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C1371" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1371" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1371" s="6">
+        <v>27</v>
+      </c>
+      <c r="F1371" s="2">
+        <v>0</v>
+      </c>
+      <c r="N1371" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI1371" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1372" ht="57.4" spans="1:35">
+      <c r="A1372" s="2">
+        <v>1368</v>
+      </c>
+      <c r="B1372" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C1372" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1372" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1372" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1372" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1372" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1373" ht="267.75" spans="1:35">
+      <c r="A1373" s="2">
+        <v>1369</v>
+      </c>
+      <c r="B1373" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C1373" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1373" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1373" s="6">
+        <v>6</v>
+      </c>
+      <c r="F1373" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1373" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1374" ht="38.25" spans="1:35">
+      <c r="A1374" s="2">
+        <v>1370</v>
+      </c>
+      <c r="B1374" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C1374" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1374" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1374" s="6">
+        <v>14</v>
+      </c>
+      <c r="F1374" s="2">
+        <v>1</v>
+      </c>
+      <c r="R1374" s="10">
+        <v>1</v>
+      </c>
+      <c r="T1374" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1375" ht="38.25" spans="1:35">
+      <c r="A1375" s="2">
+        <v>1371</v>
+      </c>
+      <c r="B1375" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C1375" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1375" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1375" s="6">
+        <v>24</v>
+      </c>
+      <c r="F1375" s="2">
+        <v>0</v>
+      </c>
+      <c r="O1375" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1376" ht="38.25" spans="1:35">
+      <c r="A1376" s="2">
+        <v>1372</v>
+      </c>
+      <c r="B1376" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C1376" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1376" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1376" s="6">
+        <v>29</v>
+      </c>
+      <c r="F1376" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC1376" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF1376" s="13">
+        <v>1</v>
+      </c>
+      <c r="AG1376" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1377" ht="76.5" spans="1:34">
+      <c r="A1377" s="2">
+        <v>1373</v>
+      </c>
+      <c r="B1377" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C1377" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1377" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1377" s="6">
+        <v>29</v>
+      </c>
+      <c r="F1377" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1377" s="8">
+        <v>1</v>
+      </c>
+      <c r="AC1377" s="12">
+        <v>1</v>
+      </c>
+      <c r="AH1377" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1378" ht="38.25" spans="1:34">
+      <c r="A1378" s="2">
+        <v>1374</v>
+      </c>
+      <c r="B1378" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C1378" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1378" s="5">
+        <v>5</v>
+      </c>
+      <c r="E1378" s="6">
+        <v>25</v>
+      </c>
+      <c r="F1378" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1378" s="8">
+        <v>1</v>
+      </c>
+      <c r="I1378" s="8">
+        <v>1</v>
+      </c>
+      <c r="O1378" s="9">
+        <v>1</v>
+      </c>
+      <c r="P1378" s="9">
+        <v>1</v>
+      </c>
+      <c r="R1378" s="10">
+        <v>1</v>
+      </c>
+      <c r="S1378" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1379" ht="324.75" spans="1:34">
+      <c r="A1379" s="2">
+        <v>1375</v>
+      </c>
+      <c r="B1379" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1379" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1379" s="5">
+        <v>5</v>
+      </c>
+      <c r="E1379" s="6">
+        <v>25</v>
+      </c>
+      <c r="F1379" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1379" s="8">
+        <v>1</v>
+      </c>
+      <c r="I1379" s="8">
+        <v>1</v>
+      </c>
+      <c r="O1379" s="9">
+        <v>1</v>
+      </c>
+      <c r="P1379" s="9">
+        <v>1</v>
+      </c>
+      <c r="R1379" s="10">
+        <v>1</v>
+      </c>
+      <c r="S1379" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1380" ht="38.25" spans="1:34">
+      <c r="A1380" s="2">
+        <v>1376</v>
+      </c>
+      <c r="B1380" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C1380" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1380" s="5">
+        <v>5</v>
+      </c>
+      <c r="E1380" s="6">
+        <v>30</v>
+      </c>
+      <c r="F1380" s="2">
+        <v>0</v>
+      </c>
+      <c r="J1380" s="8">
+        <v>1</v>
+      </c>
+      <c r="AF1380" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1381" ht="95.65" spans="1:34">
+      <c r="A1381" s="2">
+        <v>1377</v>
+      </c>
+      <c r="B1381" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1381" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1381" s="5">
+        <v>6</v>
+      </c>
+      <c r="E1381" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1381" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1381" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1381" s="8">
+        <v>1</v>
+      </c>
+      <c r="N1381" s="9">
+        <v>1</v>
+      </c>
+      <c r="P1381" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1382" ht="114.75" spans="1:34">
+      <c r="A1382" s="2">
+        <v>1378</v>
+      </c>
+      <c r="B1382" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C1382" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1382" s="5">
+        <v>6</v>
+      </c>
+      <c r="E1382" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1382" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1382" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1382" s="8">
+        <v>1</v>
+      </c>
+      <c r="N1382" s="9">
+        <v>1</v>
+      </c>
+      <c r="P1382" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1383" ht="76.5" spans="1:34">
+      <c r="A1383" s="2">
+        <v>1379</v>
+      </c>
+      <c r="B1383" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C1383" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D1383" s="5">
+        <v>6</v>
+      </c>
+      <c r="E1383" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1383" s="2">
+        <v>1</v>
+      </c>
+      <c r="G1383" s="7">
+        <v>1</v>
+      </c>
+      <c r="H1383" s="8">
+        <v>1</v>
+      </c>
+      <c r="N1383" s="9">
+        <v>1</v>
+      </c>
+      <c r="P1383" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:34">
+      <c r="A1384" s="2">
+        <v>1380</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AO1359" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AO1369" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="E846:F847">
